--- a/AAII_Financials/Yearly/CRBG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRBG_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
   <si>
     <t>CRBG</t>
   </si>
@@ -656,149 +656,161 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>25654000</v>
+        <v>17994000</v>
       </c>
       <c r="E8" s="3">
-        <v>22215000</v>
+        <v>23672000</v>
       </c>
       <c r="F8" s="3">
+        <v>22082000</v>
+      </c>
+      <c r="G8" s="3">
         <v>13990000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>12141000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14539000</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>9665000</v>
+        <v>11253000</v>
       </c>
       <c r="E9" s="3">
-        <v>10109000</v>
+        <v>8574000</v>
       </c>
       <c r="F9" s="3">
+        <v>9283000</v>
+      </c>
+      <c r="G9" s="3">
         <v>8065000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6009000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4903000</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>15989000</v>
+        <v>6741000</v>
       </c>
       <c r="E10" s="3">
-        <v>12106000</v>
+        <v>15098000</v>
       </c>
       <c r="F10" s="3">
+        <v>12799000</v>
+      </c>
+      <c r="G10" s="3">
         <v>5925000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>6132000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>9636000</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -811,8 +823,9 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -840,9 +853,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -870,39 +886,45 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-676000</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-2862000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>10000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>32000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7000</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -930,9 +952,12 @@
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -942,68 +967,75 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14660000</v>
+        <v>16480000</v>
       </c>
       <c r="E17" s="3">
-        <v>11699000</v>
+        <v>13605000</v>
       </c>
       <c r="F17" s="3">
+        <v>10886000</v>
+      </c>
+      <c r="G17" s="3">
         <v>12649000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>11447000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>14438000</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10994000</v>
+        <v>1514000</v>
       </c>
       <c r="E18" s="3">
-        <v>10516000</v>
+        <v>10067000</v>
       </c>
       <c r="F18" s="3">
+        <v>11196000</v>
+      </c>
+      <c r="G18" s="3">
         <v>1341000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>694000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>101000</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1016,19 +1048,20 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>958000</v>
       </c>
       <c r="F20" s="3">
-        <v>0</v>
+        <v>447000</v>
       </c>
       <c r="G20" s="3">
         <v>0</v>
@@ -1036,8 +1069,8 @@
       <c r="H20" s="3">
         <v>0</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
+      <c r="I20" s="3">
+        <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1045,129 +1078,144 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>12015000</v>
+        <v>1886000</v>
       </c>
       <c r="E21" s="3">
-        <v>11078000</v>
+        <v>11610000</v>
       </c>
       <c r="F21" s="3">
+        <v>12056000</v>
+      </c>
+      <c r="G21" s="3">
         <v>1666000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>988000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>193000</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>580000</v>
+      </c>
+      <c r="E22" s="3">
         <v>534000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>389000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>490000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>555000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>267000</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>10460000</v>
+        <v>940000</v>
       </c>
       <c r="E23" s="3">
-        <v>10127000</v>
+        <v>10491000</v>
       </c>
       <c r="F23" s="3">
+        <v>11254000</v>
+      </c>
+      <c r="G23" s="3">
         <v>851000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>139000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-166000</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1991000</v>
+        <v>-96000</v>
       </c>
       <c r="E24" s="3">
-        <v>1843000</v>
+        <v>2012000</v>
       </c>
       <c r="F24" s="3">
+        <v>2082000</v>
+      </c>
+      <c r="G24" s="3">
         <v>-15000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-168000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-132000</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1195,69 +1243,78 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>8469000</v>
+        <v>1036000</v>
       </c>
       <c r="E26" s="3">
-        <v>8284000</v>
+        <v>8479000</v>
       </c>
       <c r="F26" s="3">
+        <v>9172000</v>
+      </c>
+      <c r="G26" s="3">
         <v>866000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>307000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-34000</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>8149000</v>
+        <v>1104000</v>
       </c>
       <c r="E27" s="3">
-        <v>7355000</v>
+        <v>8159000</v>
       </c>
       <c r="F27" s="3">
+        <v>8243000</v>
+      </c>
+      <c r="G27" s="3">
         <v>642000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>50000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-80000</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1285,9 +1342,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1315,9 +1375,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1345,9 +1408,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1375,20 +1441,23 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-6000</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>-958000</v>
       </c>
       <c r="F32" s="3">
-        <v>0</v>
+        <v>-447000</v>
       </c>
       <c r="G32" s="3">
         <v>0</v>
@@ -1396,8 +1465,8 @@
       <c r="H32" s="3">
         <v>0</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
+      <c r="I32" s="3">
+        <v>0</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1405,39 +1474,45 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>8149000</v>
+        <v>1104000</v>
       </c>
       <c r="E33" s="3">
-        <v>7355000</v>
+        <v>8159000</v>
       </c>
       <c r="F33" s="3">
+        <v>8243000</v>
+      </c>
+      <c r="G33" s="3">
         <v>642000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>50000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-80000</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1465,74 +1540,83 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>8149000</v>
+        <v>1104000</v>
       </c>
       <c r="E35" s="3">
-        <v>7355000</v>
+        <v>8159000</v>
       </c>
       <c r="F35" s="3">
+        <v>8243000</v>
+      </c>
+      <c r="G35" s="3">
         <v>642000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>50000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-80000</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1545,8 +1629,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1559,26 +1644,27 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>612000</v>
+      </c>
+      <c r="E41" s="3">
         <v>552000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>537000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>654000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>596000</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1588,9 +1674,12 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1618,9 +1707,12 @@
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1648,9 +1740,12 @@
       <c r="K43" s="3">
         <v>0</v>
       </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1678,9 +1773,12 @@
       <c r="K44" s="3">
         <v>0</v>
       </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1708,9 +1806,12 @@
       <c r="K45" s="3">
         <v>0</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3">
+        <v>0</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1738,27 +1839,30 @@
       <c r="K46" s="3">
         <v>0</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3">
+        <v>0</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>233540000</v>
+      </c>
+      <c r="E47" s="3">
         <v>220912000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>256318000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>260274000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>238888000</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1768,24 +1872,27 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3">
         <v>43000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>51000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>63000</v>
       </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1798,9 +1905,12 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -1828,9 +1938,12 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1858,9 +1971,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1888,27 +2004,30 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>10827000</v>
+      </c>
+      <c r="E52" s="3">
         <v>8843000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4837000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3640000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3499000</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -1918,9 +2037,12 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1948,27 +2070,30 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>379270000</v>
+      </c>
+      <c r="E54" s="3">
         <v>360322000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>416212000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>410155000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>382476000</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -1978,9 +2103,12 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1993,8 +2121,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2007,8 +2136,9 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2036,23 +2166,26 @@
       <c r="K57" s="3">
         <v>0</v>
       </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>250000</v>
+      </c>
+      <c r="E58" s="3">
         <v>1500000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8317000</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
+      <c r="G58" s="3">
+        <v>0</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -2066,27 +2199,30 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>255917000</v>
+      </c>
+      <c r="E59" s="3">
         <v>243832000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>268872000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>257755000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>243341000</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2096,9 +2232,12 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2126,27 +2265,30 @@
       <c r="K60" s="3">
         <v>0</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3">
+        <v>0</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11622000</v>
+      </c>
+      <c r="E61" s="3">
         <v>13826000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>7363000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>11246000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>11078000</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2156,9 +2298,12 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2186,9 +2331,12 @@
       <c r="K62" s="3">
         <v>0</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3">
+        <v>0</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2216,9 +2364,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2246,9 +2397,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2276,27 +2430,30 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>367504000</v>
+      </c>
+      <c r="E66" s="3">
         <v>350942000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>389126000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>372923000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>350671000</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2306,9 +2463,12 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2321,8 +2481,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2350,9 +2511,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2380,9 +2544,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2410,9 +2577,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2440,27 +2610,30 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17572000</v>
+      </c>
+      <c r="E72" s="3">
         <v>18207000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>8859000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>22573000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>22476000</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2470,9 +2643,12 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2500,9 +2676,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2530,9 +2709,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2560,27 +2742,30 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11766000</v>
+      </c>
+      <c r="E76" s="3">
         <v>9380000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>27086000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>37232000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>31805000</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2590,9 +2775,12 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2620,74 +2808,83 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>8149000</v>
+        <v>1104000</v>
       </c>
       <c r="E81" s="3">
-        <v>7355000</v>
+        <v>8159000</v>
       </c>
       <c r="F81" s="3">
+        <v>8243000</v>
+      </c>
+      <c r="G81" s="3">
         <v>642000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>50000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-80000</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2700,38 +2897,42 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1021000</v>
+        <v>366000</v>
       </c>
       <c r="E83" s="3">
-        <v>562000</v>
+        <v>585000</v>
       </c>
       <c r="F83" s="3">
+        <v>413000</v>
+      </c>
+      <c r="G83" s="3">
         <v>325000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>294000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>92000</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2759,9 +2960,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2789,9 +2993,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2819,9 +3026,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2849,9 +3059,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2879,39 +3092,45 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2695000</v>
+        <v>3354000</v>
       </c>
       <c r="E89" s="3">
-        <v>2461000</v>
+        <v>2621000</v>
       </c>
       <c r="F89" s="3">
+        <v>2405000</v>
+      </c>
+      <c r="G89" s="3">
         <v>3327000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2445000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3208000</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2924,8 +3143,9 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -2953,9 +3173,12 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2983,9 +3206,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3013,39 +3239,45 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5476000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7253000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1967000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7909000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10375000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4764000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3058,17 +3290,18 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-1722000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-876000</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -3087,9 +3320,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3117,9 +3353,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3147,9 +3386,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3177,59 +3419,65 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>4600000</v>
+        <v>2114000</v>
       </c>
       <c r="E100" s="3">
-        <v>-809000</v>
+        <v>4674000</v>
       </c>
       <c r="F100" s="3">
+        <v>-753000</v>
+      </c>
+      <c r="G100" s="3">
         <v>4666000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>7919000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1539000</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-10000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7000</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -3237,37 +3485,43 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E102" s="3">
         <v>32000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-317000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>91000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-11000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17000</v>
       </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CRBG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRBG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
   <si>
     <t>CRBG</t>
   </si>
@@ -1881,11 +1881,11 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
+      <c r="D48" s="3">
+        <v>20000</v>
       </c>
       <c r="E48" s="3">
-        <v>43000</v>
+        <v>36000</v>
       </c>
       <c r="F48" s="3">
         <v>51000</v>
@@ -2209,10 +2209,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>255917000</v>
+        <v>255943000</v>
       </c>
       <c r="E59" s="3">
-        <v>243832000</v>
+        <v>243839000</v>
       </c>
       <c r="F59" s="3">
         <v>268872000</v>

--- a/AAII_Financials/Yearly/CRBG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRBG_YR_FIN.xlsx
@@ -896,13 +896,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-676000</v>
+        <v>-479000</v>
       </c>
       <c r="E14" s="3">
-        <v>1000</v>
+        <v>148000</v>
       </c>
       <c r="F14" s="3">
-        <v>-2862000</v>
+        <v>-2818000</v>
       </c>
       <c r="G14" s="3">
         <v>10000</v>

--- a/AAII_Financials/Yearly/CRBG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRBG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
   <si>
     <t>CRBG</t>
   </si>
@@ -663,8 +663,8 @@
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
@@ -700,8 +700,8 @@
       <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>3</v>
+      <c r="J7" s="2">
+        <v>36068</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>3</v>
@@ -716,25 +716,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>17994000</v>
+        <v>19083000</v>
       </c>
       <c r="E8" s="3">
-        <v>23672000</v>
+        <v>23916000</v>
       </c>
       <c r="F8" s="3">
-        <v>22082000</v>
+        <v>22927000</v>
       </c>
       <c r="G8" s="3">
-        <v>13990000</v>
+        <v>15050000</v>
       </c>
       <c r="H8" s="3">
-        <v>12141000</v>
+        <v>13210000</v>
       </c>
       <c r="I8" s="3">
-        <v>14539000</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
+        <v>15628000</v>
+      </c>
+      <c r="J8" s="3">
+        <v>2577600</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>3</v>
@@ -749,25 +749,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>11253000</v>
+        <v>15419000</v>
       </c>
       <c r="E9" s="3">
-        <v>8574000</v>
+        <v>12040000</v>
       </c>
       <c r="F9" s="3">
-        <v>9283000</v>
+        <v>12523000</v>
       </c>
       <c r="G9" s="3">
-        <v>8065000</v>
+        <v>11277000</v>
       </c>
       <c r="H9" s="3">
-        <v>6009000</v>
+        <v>10187000</v>
       </c>
       <c r="I9" s="3">
-        <v>4903000</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
+        <v>8430000</v>
+      </c>
+      <c r="J9" s="3">
+        <v>1389200</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>3</v>
@@ -782,25 +782,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>6741000</v>
+        <v>3664000</v>
       </c>
       <c r="E10" s="3">
-        <v>15098000</v>
+        <v>11876000</v>
       </c>
       <c r="F10" s="3">
-        <v>12799000</v>
+        <v>10404000</v>
       </c>
       <c r="G10" s="3">
-        <v>5925000</v>
+        <v>3773000</v>
       </c>
       <c r="H10" s="3">
-        <v>6132000</v>
+        <v>3023000</v>
       </c>
       <c r="I10" s="3">
-        <v>9636000</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
+        <v>7198000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>1188400</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>3</v>
@@ -896,19 +896,19 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-479000</v>
+        <v>-676000</v>
       </c>
       <c r="E14" s="3">
-        <v>148000</v>
+        <v>-24000</v>
       </c>
       <c r="F14" s="3">
-        <v>-2818000</v>
+        <v>-2862000</v>
       </c>
       <c r="G14" s="3">
-        <v>10000</v>
+        <v>43000</v>
       </c>
       <c r="H14" s="3">
-        <v>32000</v>
+        <v>39000</v>
       </c>
       <c r="I14" s="3">
         <v>7000</v>
@@ -929,22 +929,22 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>366000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>585000</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>413000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>325000</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>294000</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>92000</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
@@ -974,25 +974,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>16480000</v>
+        <v>18040000</v>
       </c>
       <c r="E17" s="3">
-        <v>13605000</v>
+        <v>14629000</v>
       </c>
       <c r="F17" s="3">
-        <v>10886000</v>
+        <v>14949000</v>
       </c>
       <c r="G17" s="3">
-        <v>12649000</v>
+        <v>13575000</v>
       </c>
       <c r="H17" s="3">
-        <v>11447000</v>
+        <v>12477000</v>
       </c>
       <c r="I17" s="3">
-        <v>14438000</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
+        <v>11227000</v>
+      </c>
+      <c r="J17" s="3">
+        <v>1699400</v>
       </c>
       <c r="K17" s="3" t="s">
         <v>3</v>
@@ -1007,25 +1007,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1514000</v>
+        <v>1043000</v>
       </c>
       <c r="E18" s="3">
-        <v>10067000</v>
+        <v>9287000</v>
       </c>
       <c r="F18" s="3">
-        <v>11196000</v>
+        <v>7978000</v>
       </c>
       <c r="G18" s="3">
-        <v>1341000</v>
+        <v>1475000</v>
       </c>
       <c r="H18" s="3">
-        <v>694000</v>
+        <v>733000</v>
       </c>
       <c r="I18" s="3">
-        <v>101000</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
+        <v>4401000</v>
+      </c>
+      <c r="J18" s="3">
+        <v>878100</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>3</v>
@@ -1055,22 +1055,22 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>6000</v>
+        <v>199000</v>
       </c>
       <c r="E20" s="3">
-        <v>958000</v>
+        <v>-1714000</v>
       </c>
       <c r="F20" s="3">
-        <v>447000</v>
+        <v>-803000</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
+        <v>91000</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I20" s="3">
-        <v>0</v>
+        <v>4293000</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
@@ -1088,25 +1088,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1886000</v>
+        <v>1210000</v>
       </c>
       <c r="E21" s="3">
-        <v>11610000</v>
+        <v>11586000</v>
       </c>
       <c r="F21" s="3">
-        <v>12056000</v>
+        <v>9194000</v>
       </c>
       <c r="G21" s="3">
-        <v>1666000</v>
+        <v>1709000</v>
       </c>
       <c r="H21" s="3">
-        <v>988000</v>
+        <v>1027000</v>
       </c>
       <c r="I21" s="3">
-        <v>193000</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>200000</v>
+      </c>
+      <c r="J21" s="3">
+        <v>878100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1138,8 +1138,8 @@
       <c r="I22" s="3">
         <v>267000</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
+      <c r="J22" s="3">
+        <v>129700</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>3</v>
@@ -1171,8 +1171,8 @@
       <c r="I23" s="3">
         <v>-166000</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
+      <c r="J23" s="3">
+        <v>707300</v>
       </c>
       <c r="K23" s="3" t="s">
         <v>3</v>
@@ -1204,8 +1204,8 @@
       <c r="I24" s="3">
         <v>-132000</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>191000</v>
       </c>
       <c r="K24" s="3" t="s">
         <v>3</v>
@@ -1270,8 +1270,8 @@
       <c r="I26" s="3">
         <v>-34000</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
+      <c r="J26" s="3">
+        <v>516300</v>
       </c>
       <c r="K26" s="3" t="s">
         <v>3</v>
@@ -1303,8 +1303,8 @@
       <c r="I27" s="3">
         <v>-80000</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
+      <c r="J27" s="3">
+        <v>503900</v>
       </c>
       <c r="K27" s="3" t="s">
         <v>3</v>
@@ -1451,22 +1451,22 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-6000</v>
+        <v>-199000</v>
       </c>
       <c r="E32" s="3">
-        <v>-958000</v>
+        <v>1714000</v>
       </c>
       <c r="F32" s="3">
-        <v>-447000</v>
+        <v>803000</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
+        <v>-91000</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I32" s="3">
-        <v>0</v>
+        <v>-4293000</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
@@ -1501,8 +1501,8 @@
       <c r="I33" s="3">
         <v>-80000</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
+      <c r="J33" s="3">
+        <v>516300</v>
       </c>
       <c r="K33" s="3" t="s">
         <v>3</v>
@@ -1567,8 +1567,8 @@
       <c r="I35" s="3">
         <v>-80000</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
+      <c r="J35" s="3">
+        <v>516300</v>
       </c>
       <c r="K35" s="3" t="s">
         <v>3</v>
@@ -1605,8 +1605,8 @@
       <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2" t="s">
-        <v>3</v>
+      <c r="J38" s="2">
+        <v>36068</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>3</v>
@@ -1668,8 +1668,8 @@
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
+      <c r="J41" s="3">
+        <v>1796100</v>
       </c>
       <c r="K41" s="3" t="s">
         <v>3</v>
@@ -1684,19 +1684,19 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>4333000</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>4331000</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>5414000</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>9177000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>7948000</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -1717,25 +1717,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>594000</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>916000</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>884000</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>860000</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
-      </c>
-      <c r="I43" s="3">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3">
-        <v>0</v>
+        <v>645000</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -1749,26 +1749,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1783,25 +1783,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>33030000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>31473000</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>33284000</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>33646000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
+        <v>33686000</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>297300</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -1816,25 +1816,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>38585000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>37353000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>40183000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>44601000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
-      </c>
-      <c r="I46" s="3">
-        <v>0</v>
+        <v>43106000</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>2093400</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -1849,25 +1849,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>233540000</v>
+        <v>179493000</v>
       </c>
       <c r="E47" s="3">
-        <v>220912000</v>
+        <v>169319000</v>
       </c>
       <c r="F47" s="3">
-        <v>256318000</v>
+        <v>209110000</v>
       </c>
       <c r="G47" s="3">
-        <v>260274000</v>
+        <v>205817000</v>
       </c>
       <c r="H47" s="3">
-        <v>238888000</v>
+        <v>184976000</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
+      <c r="J47" s="3">
+        <v>20803200</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
@@ -1881,17 +1881,17 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
-        <v>20000</v>
-      </c>
-      <c r="E48" s="3">
-        <v>36000</v>
-      </c>
-      <c r="F48" s="3">
-        <v>51000</v>
-      </c>
-      <c r="G48" s="3">
-        <v>63000</v>
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1915,25 +1915,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>0</v>
+        <v>10011000</v>
       </c>
       <c r="E49" s="3">
-        <v>0</v>
+        <v>10563000</v>
       </c>
       <c r="F49" s="3">
-        <v>0</v>
+        <v>8058000</v>
       </c>
       <c r="G49" s="3">
-        <v>0</v>
+        <v>7363000</v>
       </c>
       <c r="H49" s="3">
-        <v>0</v>
-      </c>
-      <c r="I49" s="3">
-        <v>0</v>
+        <v>8069000</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J49" s="3">
-        <v>0</v>
+        <v>996500</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -2014,25 +2014,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>10827000</v>
+        <v>95737000</v>
       </c>
       <c r="E52" s="3">
-        <v>8843000</v>
+        <v>89690000</v>
       </c>
       <c r="F52" s="3">
-        <v>4837000</v>
+        <v>114636000</v>
       </c>
       <c r="G52" s="3">
-        <v>3640000</v>
+        <v>110420000</v>
       </c>
       <c r="H52" s="3">
-        <v>3499000</v>
+        <v>104170000</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
+      <c r="J52" s="3">
+        <v>11894800</v>
       </c>
       <c r="K52" s="3" t="s">
         <v>3</v>
@@ -2097,8 +2097,8 @@
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
+      <c r="J54" s="3">
+        <v>39200400</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>3</v>
@@ -2142,26 +2142,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -2187,14 +2187,14 @@
       <c r="G58" s="3">
         <v>0</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
+      <c r="H58" s="3">
+        <v>0</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+      <c r="J58" s="3">
+        <v>556300</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2209,25 +2209,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>255943000</v>
+        <v>27844000</v>
       </c>
       <c r="E59" s="3">
-        <v>243839000</v>
+        <v>26648000</v>
       </c>
       <c r="F59" s="3">
-        <v>268872000</v>
+        <v>35335000</v>
       </c>
       <c r="G59" s="3">
-        <v>257755000</v>
+        <v>44785000</v>
       </c>
       <c r="H59" s="3">
-        <v>243341000</v>
+        <v>39820000</v>
       </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
+      <c r="J59" s="3">
+        <v>2700</v>
       </c>
       <c r="K59" s="3" t="s">
         <v>3</v>
@@ -2242,25 +2242,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>28094000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>28148000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>43652000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>44785000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
+        <v>39820000</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>558900</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>1155200</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -2308,25 +2308,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>0</v>
+        <v>326919000</v>
       </c>
       <c r="E62" s="3">
-        <v>0</v>
+        <v>308029000</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>336269000</v>
       </c>
       <c r="G62" s="3">
-        <v>0</v>
+        <v>314292000</v>
       </c>
       <c r="H62" s="3">
-        <v>0</v>
-      </c>
-      <c r="I62" s="3">
-        <v>0</v>
+        <v>297899000</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J62" s="3">
-        <v>0</v>
+        <v>34099300</v>
       </c>
       <c r="K62" s="3">
         <v>0</v>
@@ -2440,25 +2440,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>367504000</v>
+        <v>366635000</v>
       </c>
       <c r="E66" s="3">
-        <v>350942000</v>
+        <v>350003000</v>
       </c>
       <c r="F66" s="3">
-        <v>389126000</v>
+        <v>387284000</v>
       </c>
       <c r="G66" s="3">
-        <v>372923000</v>
+        <v>370323000</v>
       </c>
       <c r="H66" s="3">
-        <v>350671000</v>
+        <v>348797000</v>
       </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
+      <c r="J66" s="3">
+        <v>36208300</v>
       </c>
       <c r="K66" s="3" t="s">
         <v>3</v>
@@ -2572,7 +2572,7 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>248000</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -2628,17 +2628,17 @@
       <c r="F72" s="3">
         <v>8859000</v>
       </c>
-      <c r="G72" s="3">
-        <v>22573000</v>
-      </c>
-      <c r="H72" s="3">
-        <v>22476000</v>
+      <c r="G72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>3</v>
+      <c r="J72" s="3">
+        <v>1596200</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>3</v>
@@ -2769,8 +2769,8 @@
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
+      <c r="J76" s="3">
+        <v>2744100</v>
       </c>
       <c r="K76" s="3" t="s">
         <v>3</v>
@@ -2840,8 +2840,8 @@
       <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2" t="s">
-        <v>3</v>
+      <c r="J80" s="2">
+        <v>36068</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>3</v>
@@ -2873,8 +2873,8 @@
       <c r="I81" s="3">
         <v>-80000</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
+      <c r="J81" s="3">
+        <v>516300</v>
       </c>
       <c r="K81" s="3" t="s">
         <v>3</v>
@@ -3102,7 +3102,7 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3354000</v>
+        <v>3357000</v>
       </c>
       <c r="E89" s="3">
         <v>2621000</v>
@@ -3119,8 +3119,8 @@
       <c r="I89" s="3">
         <v>3208000</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
+      <c r="J89" s="3">
+        <v>1561200</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -3149,26 +3149,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3266,8 +3266,8 @@
       <c r="I94" s="3">
         <v>-4764000</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="J94" s="3">
+        <v>-1036400</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -3297,22 +3297,22 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1722000</v>
+        <v>586800</v>
       </c>
       <c r="E96" s="3">
-        <v>-876000</v>
+        <v>876000</v>
       </c>
       <c r="F96" s="3">
-        <v>0</v>
+        <v>1577000</v>
       </c>
       <c r="G96" s="3">
-        <v>0</v>
+        <v>472000</v>
       </c>
       <c r="H96" s="3">
-        <v>0</v>
+        <v>1624000</v>
       </c>
       <c r="I96" s="3">
-        <v>0</v>
+        <v>2657000</v>
       </c>
       <c r="J96" s="3">
         <v>0</v>
@@ -3446,8 +3446,8 @@
       <c r="I100" s="3">
         <v>1539000</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+      <c r="J100" s="3">
+        <v>278000</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -3473,11 +3473,11 @@
       <c r="G101" s="3">
         <v>7000</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -3495,7 +3495,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-8000</v>
+        <v>-2000</v>
       </c>
       <c r="E102" s="3">
         <v>32000</v>
@@ -3512,8 +3512,8 @@
       <c r="I102" s="3">
         <v>-17000</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+      <c r="J102" s="3">
+        <v>802800</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/CRBG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRBG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
   <si>
     <t>CRBG</t>
   </si>
@@ -656,161 +656,173 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>36068</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>18640000</v>
+      </c>
+      <c r="E8" s="3">
         <v>19083000</v>
       </c>
-      <c r="E8" s="3">
-        <v>23916000</v>
-      </c>
       <c r="F8" s="3">
+        <v>23941000</v>
+      </c>
+      <c r="G8" s="3">
         <v>22927000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>15050000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>13210000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>15628000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2577600</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>13520000</v>
+      </c>
+      <c r="E9" s="3">
         <v>15419000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12040000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12523000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11277000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>10187000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8430000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1389200</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>5120000</v>
+      </c>
+      <c r="E10" s="3">
         <v>3664000</v>
       </c>
-      <c r="E10" s="3">
-        <v>11876000</v>
-      </c>
       <c r="F10" s="3">
+        <v>11901000</v>
+      </c>
+      <c r="G10" s="3">
         <v>10404000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3773000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3023000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>7198000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1188400</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -824,8 +836,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -856,9 +869,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -889,75 +905,84 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-245000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-676000</v>
       </c>
-      <c r="E14" s="3">
-        <v>-24000</v>
-      </c>
       <c r="F14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="3">
         <v>-2862000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>43000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>39000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>193000</v>
+      </c>
+      <c r="E15" s="3">
         <v>366000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>585000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>413000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>325000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>294000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>92000</v>
       </c>
-      <c r="J15" s="3">
-        <v>0</v>
-      </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -968,74 +993,81 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>15896000</v>
+      </c>
+      <c r="E17" s="3">
         <v>18040000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>14629000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14949000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13575000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>12477000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11227000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1699400</v>
       </c>
-      <c r="K17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>2744000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1043000</v>
       </c>
-      <c r="E18" s="3">
-        <v>9287000</v>
-      </c>
       <c r="F18" s="3">
+        <v>9312000</v>
+      </c>
+      <c r="G18" s="3">
         <v>7978000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1475000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>733000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>4401000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>878100</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1049,173 +1081,189 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-368000</v>
+      </c>
+      <c r="E20" s="3">
         <v>199000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1714000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-803000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>91000</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="I20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3">
         <v>4293000</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>3305000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1210000</v>
       </c>
-      <c r="E21" s="3">
-        <v>11586000</v>
-      </c>
       <c r="F21" s="3">
+        <v>11611000</v>
+      </c>
+      <c r="G21" s="3">
         <v>9194000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1709000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1027000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>200000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>878100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>554000</v>
+      </c>
+      <c r="E22" s="3">
         <v>580000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>534000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>389000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>490000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>555000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>267000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>129700</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2803000</v>
+      </c>
+      <c r="E23" s="3">
         <v>940000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>10491000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>11254000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>851000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>139000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-166000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>707300</v>
       </c>
-      <c r="K23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>600000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-96000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2012000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2082000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-15000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-168000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-132000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>191000</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1246,75 +1294,84 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2203000</v>
+      </c>
+      <c r="E26" s="3">
         <v>1036000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>8479000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>9172000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>866000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>307000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-34000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>516300</v>
       </c>
-      <c r="K26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2230000</v>
+      </c>
+      <c r="E27" s="3">
         <v>1104000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>8159000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8243000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>642000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>50000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-80000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>503900</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1345,9 +1402,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1378,9 +1438,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1411,9 +1474,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1444,75 +1510,84 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>368000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-199000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1714000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>803000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-91000</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="I32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3">
         <v>-4293000</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2230000</v>
+      </c>
+      <c r="E33" s="3">
         <v>1104000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>8159000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8243000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>642000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>50000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-80000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>516300</v>
       </c>
-      <c r="K33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1543,80 +1618,89 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2230000</v>
+      </c>
+      <c r="E35" s="3">
         <v>1104000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>8159000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8243000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>642000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>50000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-80000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>516300</v>
       </c>
-      <c r="K35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>36068</v>
       </c>
-      <c r="K38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1630,8 +1714,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1645,62 +1730,66 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>806000</v>
+      </c>
+      <c r="E41" s="3">
         <v>612000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>552000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>537000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>654000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>596000</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J41" s="3">
+      <c r="J41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K41" s="3">
         <v>1796100</v>
       </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>4977000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4333000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4331000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5414000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>9177000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>7948000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
         <v>0</v>
       </c>
@@ -1710,42 +1799,48 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>713000</v>
+      </c>
+      <c r="E43" s="3">
         <v>594000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>916000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>884000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>860000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>645000</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
+      <c r="K43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1770,114 +1865,126 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
       </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>29053000</v>
+      </c>
+      <c r="E45" s="3">
         <v>33030000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>31473000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>33284000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33646000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33686000</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J45" s="3">
+      <c r="J45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K45" s="3">
         <v>297300</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>38585000</v>
+        <v>35553000</v>
       </c>
       <c r="E46" s="3">
+        <v>38572000</v>
+      </c>
+      <c r="F46" s="3">
         <v>37353000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>40183000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>44601000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>43106000</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J46" s="3">
+      <c r="J46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K46" s="3">
         <v>2093400</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>184583000</v>
+      </c>
+      <c r="E47" s="3">
         <v>179493000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>169319000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>209110000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>205817000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>184976000</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>20803200</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -1908,42 +2015,48 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>10293000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10011000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10563000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8058000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7363000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>8069000</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J49" s="3">
+      <c r="J49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K49" s="3">
         <v>996500</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1974,9 +2087,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2007,42 +2123,48 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>95737000</v>
+        <v>98297000</v>
       </c>
       <c r="E52" s="3">
+        <v>95750000</v>
+      </c>
+      <c r="F52" s="3">
         <v>89690000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>114636000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>110420000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>104170000</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="J52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K52" s="3">
         <v>11894800</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2073,42 +2195,48 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>389397000</v>
+      </c>
+      <c r="E54" s="3">
         <v>379270000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>360322000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>416212000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>410155000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>382476000</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J54" s="3">
+      <c r="J54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K54" s="3">
         <v>39200400</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2122,8 +2250,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2137,8 +2266,9 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2163,180 +2293,198 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
       </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>250000</v>
+        <v>10518000</v>
       </c>
       <c r="E58" s="3">
+        <v>9368000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1500000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8317000</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3">
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K58" s="3">
         <v>556300</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>24401000</v>
+      </c>
+      <c r="E59" s="3">
         <v>27844000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>26648000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>35335000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>44785000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>39820000</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J59" s="3">
+      <c r="J59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K59" s="3">
         <v>2700</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>28094000</v>
+        <v>34919000</v>
       </c>
       <c r="E60" s="3">
+        <v>37212000</v>
+      </c>
+      <c r="F60" s="3">
         <v>28148000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>43652000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>44785000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>39820000</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J60" s="3">
+      <c r="J60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K60" s="3">
         <v>558900</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3">
+        <v>0</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11622000</v>
+        <v>1954000</v>
       </c>
       <c r="E61" s="3">
-        <v>13826000</v>
+        <v>2530000</v>
       </c>
       <c r="F61" s="3">
-        <v>7363000</v>
+        <v>13869000</v>
       </c>
       <c r="G61" s="3">
+        <v>7429000</v>
+      </c>
+      <c r="H61" s="3">
         <v>11246000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11078000</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
+        <v>0</v>
+      </c>
+      <c r="K61" s="3">
         <v>1155200</v>
       </c>
-      <c r="K61" s="3">
-        <v>0</v>
-      </c>
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>326919000</v>
+        <v>340198000</v>
       </c>
       <c r="E62" s="3">
-        <v>308029000</v>
+        <v>326893000</v>
       </c>
       <c r="F62" s="3">
-        <v>336269000</v>
+        <v>307986000</v>
       </c>
       <c r="G62" s="3">
+        <v>336203000</v>
+      </c>
+      <c r="H62" s="3">
         <v>314292000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>297899000</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="J62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K62" s="3">
         <v>34099300</v>
       </c>
-      <c r="K62" s="3">
-        <v>0</v>
-      </c>
       <c r="L62" s="3">
         <v>0</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3">
+        <v>0</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2367,9 +2515,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2400,9 +2551,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2433,42 +2587,48 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>377071000</v>
+      </c>
+      <c r="E66" s="3">
         <v>366635000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>350003000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>387284000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>370323000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>348797000</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J66" s="3">
+      <c r="J66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K66" s="3">
         <v>36208300</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2482,8 +2642,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2514,9 +2675,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2547,9 +2711,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2572,17 +2739,20 @@
         <v>0</v>
       </c>
       <c r="J70" s="3">
+        <v>0</v>
+      </c>
+      <c r="K70" s="3">
         <v>248000</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2613,42 +2783,48 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>19257000</v>
+      </c>
+      <c r="E72" s="3">
         <v>17572000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18207000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8859000</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="J72" s="3">
+      <c r="J72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K72" s="3">
         <v>1596200</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2679,9 +2855,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2712,9 +2891,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2745,42 +2927,48 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>11462000</v>
+      </c>
+      <c r="E76" s="3">
         <v>11766000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>9380000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>27086000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>37232000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>31805000</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J76" s="3">
+      <c r="J76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K76" s="3">
         <v>2744100</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2811,80 +2999,89 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>36068</v>
       </c>
-      <c r="K80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2230000</v>
+      </c>
+      <c r="E81" s="3">
         <v>1104000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>8159000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8243000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>642000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>50000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-80000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>516300</v>
       </c>
-      <c r="K81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2898,41 +3095,45 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>193000</v>
+      </c>
+      <c r="E83" s="3">
         <v>366000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>585000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>413000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>325000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>294000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>92000</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2963,9 +3164,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2996,9 +3200,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3029,9 +3236,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3062,9 +3272,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3095,42 +3308,48 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2151000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3357000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>2621000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2405000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3327000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2445000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3208000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1561200</v>
       </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3144,8 +3363,9 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3170,15 +3390,18 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3209,9 +3432,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3242,42 +3468,48 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-11536000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5476000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7253000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1967000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7909000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10375000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4764000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1036400</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3291,41 +3523,45 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>586800</v>
+        <v>544000</v>
       </c>
       <c r="E96" s="3">
+        <v>1722000</v>
+      </c>
+      <c r="F96" s="3">
         <v>876000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1577000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>472000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1624000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2657000</v>
       </c>
-      <c r="J96" s="3">
-        <v>0</v>
-      </c>
       <c r="K96" s="3">
         <v>0</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3356,9 +3592,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3389,9 +3628,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3422,60 +3664,66 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>9580000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2114000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>4674000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-753000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4666000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>7919000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1539000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>278000</v>
       </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E101" s="3">
         <v>3000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-10000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-2000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>7000</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3488,40 +3736,46 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>196000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>32000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-317000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>91000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-11000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>802800</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CRBG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRBG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
   <si>
     <t>CRBG</t>
   </si>
@@ -1988,11 +1988,11 @@
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
+      <c r="D48" s="3">
+        <v>75000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>20000</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>3</v>
@@ -2133,10 +2133,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>98297000</v>
+        <v>98222000</v>
       </c>
       <c r="E52" s="3">
-        <v>95750000</v>
+        <v>95730000</v>
       </c>
       <c r="F52" s="3">
         <v>89690000</v>
@@ -2309,22 +2309,22 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>10518000</v>
+        <v>4165000</v>
       </c>
       <c r="E58" s="3">
-        <v>9368000</v>
+        <v>2750000</v>
       </c>
       <c r="F58" s="3">
-        <v>1500000</v>
+        <v>4600000</v>
       </c>
       <c r="G58" s="3">
-        <v>8317000</v>
+        <v>12017000</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>3700000</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>3100000</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
@@ -2357,10 +2357,10 @@
         <v>35335000</v>
       </c>
       <c r="H59" s="3">
-        <v>44785000</v>
+        <v>36789000</v>
       </c>
       <c r="I59" s="3">
-        <v>39820000</v>
+        <v>34433000</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
@@ -2381,22 +2381,22 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>34919000</v>
+        <v>28566000</v>
       </c>
       <c r="E60" s="3">
-        <v>37212000</v>
+        <v>30594000</v>
       </c>
       <c r="F60" s="3">
-        <v>28148000</v>
+        <v>31248000</v>
       </c>
       <c r="G60" s="3">
-        <v>43652000</v>
+        <v>47352000</v>
       </c>
       <c r="H60" s="3">
-        <v>44785000</v>
+        <v>40489000</v>
       </c>
       <c r="I60" s="3">
-        <v>39820000</v>
+        <v>37533000</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
@@ -2417,10 +2417,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1954000</v>
+        <v>11307000</v>
       </c>
       <c r="E61" s="3">
-        <v>2530000</v>
+        <v>11648000</v>
       </c>
       <c r="F61" s="3">
         <v>13869000</v>
@@ -2453,22 +2453,22 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>340198000</v>
+        <v>337198000</v>
       </c>
       <c r="E62" s="3">
-        <v>326893000</v>
+        <v>324393000</v>
       </c>
       <c r="F62" s="3">
-        <v>307986000</v>
+        <v>304886000</v>
       </c>
       <c r="G62" s="3">
-        <v>336203000</v>
+        <v>332503000</v>
       </c>
       <c r="H62" s="3">
-        <v>314292000</v>
+        <v>318588000</v>
       </c>
       <c r="I62" s="3">
-        <v>297899000</v>
+        <v>300186000</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/CRBG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CRBG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="92">
   <si>
     <t>CRBG</t>
   </si>
@@ -656,173 +656,185 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="10" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>36068</v>
       </c>
-      <c r="L7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>18640000</v>
+        <v>18617000</v>
       </c>
       <c r="E8" s="3">
-        <v>19083000</v>
+        <v>18566000</v>
       </c>
       <c r="F8" s="3">
+        <v>19005000</v>
+      </c>
+      <c r="G8" s="3">
         <v>23941000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22927000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>15050000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>13210000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15628000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2577600</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>15709000</v>
+      </c>
+      <c r="E9" s="3">
         <v>13520000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15419000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12040000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12523000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11277000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>10187000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8430000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1389200</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>5120000</v>
+        <v>2908000</v>
       </c>
       <c r="E10" s="3">
-        <v>3664000</v>
+        <v>5046000</v>
       </c>
       <c r="F10" s="3">
+        <v>3586000</v>
+      </c>
+      <c r="G10" s="3">
         <v>11901000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>10404000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3773000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3023000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>7198000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1188400</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -837,8 +849,9 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -872,9 +885,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -908,81 +924,90 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>-245000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-676000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-2862000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>43000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>39000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>556000</v>
+      </c>
+      <c r="E15" s="3">
         <v>193000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>366000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>585000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>413000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>325000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>294000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>92000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -994,80 +1019,87 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>15896000</v>
+        <v>17986000</v>
       </c>
       <c r="E17" s="3">
-        <v>18040000</v>
+        <v>15822000</v>
       </c>
       <c r="F17" s="3">
+        <v>17962000</v>
+      </c>
+      <c r="G17" s="3">
         <v>14629000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>14949000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13575000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>12477000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11227000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1699400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>631000</v>
+      </c>
+      <c r="E18" s="3">
         <v>2744000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1043000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>9312000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7978000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1475000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>733000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4401000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>878100</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1082,188 +1114,204 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>620000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-368000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>199000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1714000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-803000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>91000</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="3">
         <v>4293000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>567000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3305000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1210000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11611000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>9194000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1709000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1027000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>200000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>878100</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>552000</v>
+      </c>
+      <c r="E22" s="3">
         <v>554000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>580000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>534000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>389000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>490000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>555000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>267000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>129700</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-541000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2803000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>940000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>10491000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>11254000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>851000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>139000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-166000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>707300</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-151000</v>
+      </c>
+      <c r="E24" s="3">
         <v>600000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-96000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>2012000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2082000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-15000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-168000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-132000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>191000</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1297,81 +1345,90 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-390000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2203000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>1036000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>8479000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>9172000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>866000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>307000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-34000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>516300</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-366000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2230000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1104000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>8159000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>8243000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>642000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>50000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-80000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>503900</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1405,9 +1462,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1441,9 +1501,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1477,9 +1540,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1513,81 +1579,90 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-620000</v>
+      </c>
+      <c r="E32" s="3">
         <v>368000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-199000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1714000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>803000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-91000</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K32" s="3">
         <v>-4293000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-366000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2230000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>1104000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>8159000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>8243000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>642000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>50000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-80000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>516300</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1621,86 +1696,95 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-366000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2230000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>1104000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>8159000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>8243000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>642000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>50000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-80000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>516300</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>36068</v>
       </c>
-      <c r="L38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1715,8 +1799,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1731,68 +1816,72 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>447000</v>
+      </c>
+      <c r="E41" s="3">
         <v>806000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>612000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>552000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>537000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>654000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>596000</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K41" s="3">
+      <c r="K41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L41" s="3">
         <v>1796100</v>
       </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5671000</v>
+      </c>
+      <c r="E42" s="3">
         <v>4977000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>4333000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>4331000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5414000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>9177000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7948000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -1802,45 +1891,51 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>648000</v>
+      </c>
+      <c r="E43" s="3">
         <v>713000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>594000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>916000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>884000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>860000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>645000</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
+      <c r="L43" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1868,135 +1963,147 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>29053000</v>
+        <v>28871000</v>
       </c>
       <c r="E45" s="3">
+        <v>28855000</v>
+      </c>
+      <c r="F45" s="3">
         <v>33030000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>31473000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>33284000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>33646000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>33686000</v>
       </c>
-      <c r="J45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L45" s="3">
         <v>297300</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>35553000</v>
+        <v>35641000</v>
       </c>
       <c r="E46" s="3">
+        <v>35355000</v>
+      </c>
+      <c r="F46" s="3">
         <v>38572000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>37353000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>40183000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>44601000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>43106000</v>
       </c>
-      <c r="J46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K46" s="3">
+      <c r="K46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L46" s="3">
         <v>2093400</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3">
+        <v>0</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>204117000</v>
+      </c>
+      <c r="E47" s="3">
         <v>184583000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>179493000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>169319000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>209110000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>205817000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>184976000</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>20803200</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>79000</v>
+      </c>
+      <c r="E48" s="3">
         <v>75000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>20000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2018,45 +2125,51 @@
       <c r="M48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>8885000</v>
+      </c>
+      <c r="E49" s="3">
         <v>10293000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10011000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>10563000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>8058000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7363000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>8069000</v>
       </c>
-      <c r="J49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K49" s="3">
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3">
         <v>996500</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
       <c r="M49" s="3">
         <v>0</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2090,9 +2203,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2126,45 +2242,51 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>98222000</v>
+        <v>102877000</v>
       </c>
       <c r="E52" s="3">
+        <v>98420000</v>
+      </c>
+      <c r="F52" s="3">
         <v>95730000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>89690000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>114636000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>110420000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>104170000</v>
       </c>
-      <c r="J52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="3">
         <v>11894800</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2198,45 +2320,51 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>413547000</v>
+      </c>
+      <c r="E54" s="3">
         <v>389397000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>379270000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>360322000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>416212000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>410155000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>382476000</v>
       </c>
-      <c r="J54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K54" s="3">
+      <c r="K54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="3">
         <v>39200400</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2251,8 +2379,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2267,8 +2396,9 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2296,195 +2426,213 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>4165000</v>
+        <v>4518000</v>
       </c>
       <c r="E58" s="3">
+        <v>4101000</v>
+      </c>
+      <c r="F58" s="3">
         <v>2750000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4600000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12017000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3700000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3100000</v>
       </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K58" s="3">
+      <c r="K58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="3">
         <v>556300</v>
       </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>23947000</v>
+      </c>
+      <c r="E59" s="3">
         <v>24401000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>27844000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>26648000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>35335000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>36789000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>34433000</v>
       </c>
-      <c r="J59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K59" s="3">
+      <c r="K59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L59" s="3">
         <v>2700</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>28566000</v>
+        <v>28465000</v>
       </c>
       <c r="E60" s="3">
+        <v>28502000</v>
+      </c>
+      <c r="F60" s="3">
         <v>30594000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>31248000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47352000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>40489000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>37533000</v>
       </c>
-      <c r="J60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K60" s="3">
+      <c r="K60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L60" s="3">
         <v>558900</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>11307000</v>
+        <v>10968000</v>
       </c>
       <c r="E61" s="3">
+        <v>11371000</v>
+      </c>
+      <c r="F61" s="3">
         <v>11648000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>13869000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7429000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11246000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11078000</v>
       </c>
-      <c r="J61" s="3">
-        <v>0</v>
-      </c>
       <c r="K61" s="3">
+        <v>0</v>
+      </c>
+      <c r="L61" s="3">
         <v>1155200</v>
       </c>
-      <c r="L61" s="3">
-        <v>0</v>
-      </c>
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>360154000</v>
+      </c>
+      <c r="E62" s="3">
         <v>337198000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>324393000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>304886000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>332503000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>318588000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>300186000</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L62" s="3">
         <v>34099300</v>
       </c>
-      <c r="L62" s="3">
-        <v>0</v>
-      </c>
       <c r="M62" s="3">
         <v>0</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3">
+        <v>0</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2518,9 +2666,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2554,9 +2705,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2590,45 +2744,51 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>399587000</v>
+      </c>
+      <c r="E66" s="3">
         <v>377071000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>366635000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>350003000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>387284000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>370323000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>348797000</v>
       </c>
-      <c r="J66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K66" s="3">
+      <c r="K66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L66" s="3">
         <v>36208300</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2643,8 +2803,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2678,9 +2839,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2714,14 +2878,17 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>493000</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -2742,17 +2909,20 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>248000</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2786,45 +2956,51 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18373000</v>
+      </c>
+      <c r="E72" s="3">
         <v>19257000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>17572000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>18207000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>8859000</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="3">
         <v>1596200</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2858,9 +3034,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2894,9 +3073,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2930,45 +3112,51 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12708000</v>
+      </c>
+      <c r="E76" s="3">
         <v>11462000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>11766000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>9380000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>27086000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>37232000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>31805000</v>
       </c>
-      <c r="J76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K76" s="3">
+      <c r="K76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="3">
         <v>2744100</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3002,86 +3190,95 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>36068</v>
       </c>
-      <c r="L80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-366000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2230000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>1104000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>8159000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>8243000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>642000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>50000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-80000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>516300</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3096,44 +3293,48 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>556000</v>
+      </c>
+      <c r="E83" s="3">
         <v>193000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>366000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>585000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>413000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>325000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>294000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>92000</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3167,9 +3368,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3203,9 +3407,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3239,9 +3446,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3275,9 +3485,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3311,45 +3524,51 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2021000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2151000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3357000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2621000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2405000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>3327000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>2445000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3208000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1561200</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3364,8 +3583,9 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3393,15 +3613,18 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3435,9 +3658,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3471,45 +3697,51 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13332000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11536000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-5476000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7253000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1967000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7909000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10375000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4764000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1036400</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3524,44 +3756,48 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>511000</v>
+      </c>
+      <c r="E96" s="3">
         <v>544000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1722000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>876000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1577000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>472000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1624000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2657000</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
       <c r="L96" s="3">
         <v>0</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3595,9 +3831,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3631,9 +3870,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3667,45 +3909,51 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>10939000</v>
+      </c>
+      <c r="E100" s="3">
         <v>9580000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2114000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>4674000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-753000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>4666000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>7919000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1539000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>278000</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3713,20 +3961,20 @@
         <v>1000</v>
       </c>
       <c r="E101" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F101" s="3">
         <v>3000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-10000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-2000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7000</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3739,43 +3987,49 @@
       <c r="M101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-371000</v>
+      </c>
+      <c r="E102" s="3">
         <v>196000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>32000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-317000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>91000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-11000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>802800</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
